--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4B578D-3CB3-439D-B4A3-4DF7CDF38F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9454AEC-DBB7-49F4-AB5D-9B317E6ACB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>leader_name</t>
   </si>
@@ -36,20 +36,38 @@
     <t>end_date</t>
   </si>
   <si>
+    <t>Devendra Fadnavis</t>
+  </si>
+  <si>
+    <t>Ashish Shelar</t>
+  </si>
+  <si>
+    <t>08-25-2025</t>
+  </si>
+  <si>
     <t>facebook_excel_file_path</t>
   </si>
   <si>
-    <t>Devendra Fadnavis</t>
-  </si>
-  <si>
-    <t>08-18-2025</t>
+    <t>Prakash Abitkar</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule</t>
+  </si>
+  <si>
+    <t>Eknath Shinde</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +85,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -89,15 +115,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -376,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -396,18 +425,85 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45666</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45666</v>
       </c>
     </row>
   </sheetData>

--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9454AEC-DBB7-49F4-AB5D-9B317E6ACB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FB03C8-E7B6-4AA0-B89C-C3223FB75851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>leader_name</t>
   </si>
@@ -36,28 +36,19 @@
     <t>end_date</t>
   </si>
   <si>
-    <t>Devendra Fadnavis</t>
+    <t>facebook_profile_url</t>
   </si>
   <si>
     <t>Ashish Shelar</t>
   </si>
   <si>
-    <t>08-25-2025</t>
-  </si>
-  <si>
-    <t>facebook_excel_file_path</t>
+    <t>https://www.facebook.com/AdvocateAshishShelar</t>
   </si>
   <si>
     <t>Prakash Abitkar</t>
   </si>
   <si>
-    <t>Ravindra Chavan</t>
-  </si>
-  <si>
-    <t>Chandrakant Patil</t>
-  </si>
-  <si>
-    <t>Chandrashekhar Bawankule</t>
+    <t>https://www.facebook.com/PrakashAbitkar1600</t>
   </si>
   <si>
     <t>Eknath Shinde</t>
@@ -405,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -425,90 +416,55 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45904</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45904</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
-        <v>45666</v>
-      </c>
-      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45904</v>
       </c>
       <c r="C3" s="2">
-        <v>45666</v>
+        <v>45904</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45904</v>
       </c>
       <c r="C4" s="2">
-        <v>45666</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>45666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45666</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>45666</v>
+        <v>45904</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{9F21FA8A-6254-4424-9567-D3CCC5C923A8}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{D0E96ECC-FD66-4FF0-9864-86833E0F2A05}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FB03C8-E7B6-4AA0-B89C-C3223FB75851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C0A58C-F2A4-457A-A65F-9307FBE274EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>leader_name</t>
   </si>
@@ -52,13 +53,40 @@
   </si>
   <si>
     <t>Eknath Shinde</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ravindrachavanofficial</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ChDadaPatil</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ckbawankule</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan</t>
+  </si>
+  <si>
+    <t>OBC Andolan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,6 +116,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -110,11 +144,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -396,10 +433,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
@@ -421,50 +458,142 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45903</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45905</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF8F8C7-ECA9-4044-81E7-0CA852586859}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45908</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45904</v>
+        <v>45901</v>
       </c>
       <c r="C2" s="2">
-        <v>45904</v>
+        <v>45908</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45908</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2">
-        <v>45904</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45904</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
       <c r="B4" s="2">
-        <v>45904</v>
+        <v>45901</v>
       </c>
       <c r="C4" s="2">
-        <v>45904</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>45908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45908</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45908</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45908</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45908</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{9F21FA8A-6254-4424-9567-D3CCC5C923A8}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{D0E96ECC-FD66-4FF0-9864-86833E0F2A05}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{78B36FED-FC4F-48FD-B7FE-B84FB456F631}"/>
+    <hyperlink ref="D1" r:id="rId2" xr:uid="{2C9F7730-B5AB-4327-B53B-BEF0B1AC250B}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{992277C5-361B-4E2A-B687-E1C2C4B5D535}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{99703584-4C05-41F4-A3C0-44F255B253C1}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{E20DDFD9-D127-4AB6-B1B8-09FD68386E74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C0A58C-F2A4-457A-A65F-9307FBE274EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8528D347-A2CC-4767-8DFF-5D2A27D3F63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>leader_name</t>
   </si>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
@@ -467,10 +467,27 @@
         <v>45905</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45901</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45908</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{55EF77D0-7996-4AD8-86B1-5C9F5E16CF6A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8528D347-A2CC-4767-8DFF-5D2A27D3F63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F55145-6FB5-4E24-8477-AA420DC84806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>leader_name</t>
   </si>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
@@ -458,13 +458,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>45903</v>
+        <v>45908</v>
       </c>
       <c r="C2" s="2">
-        <v>45905</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -472,28 +472,110 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>45901</v>
+        <v>45908</v>
       </c>
       <c r="C3" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45915</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{55EF77D0-7996-4AD8-86B1-5C9F5E16CF6A}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{ED579688-13B9-41DF-9417-A11CACC9FD09}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{B6EE4731-DACA-44BD-B321-3D37BDB35EF3}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{726232BE-FFF7-48BF-96A3-E31918FE2BBF}"/>
+    <hyperlink ref="D7" r:id="rId4" xr:uid="{4AF10226-85EC-4E10-8D35-ED72C6A663DC}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{17299730-F797-4499-AF48-DD4C0EF94E5D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF8F8C7-ECA9-4044-81E7-0CA852586859}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -601,6 +683,17 @@
       </c>
       <c r="C8" s="2">
         <v>45908</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45903</v>
+      </c>
+      <c r="C10" s="2">
+        <v>45905</v>
       </c>
     </row>
   </sheetData>

--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -8,25 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F55145-6FB5-4E24-8477-AA420DC84806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F82066-C05C-485A-83BB-0FE5CF955F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t>leader_name</t>
   </si>
@@ -80,6 +92,18 @@
   </si>
   <si>
     <t>OBC Andolan</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/JaykumarGoreSpeaks</t>
+  </si>
+  <si>
+    <t>Mahsul</t>
+  </si>
+  <si>
+    <t>Panchayat Raj</t>
   </si>
 </sst>
 </file>
@@ -461,52 +485,52 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C2" s="2">
-        <v>45915</v>
+        <v>45922</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C3" s="2">
-        <v>45915</v>
+        <v>45922</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C4" s="2">
-        <v>45915</v>
+        <v>45922</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C5" s="2">
-        <v>45915</v>
+        <v>45922</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -514,10 +538,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C6" s="2">
-        <v>45915</v>
+        <v>45922</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -525,10 +549,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C7" s="2">
-        <v>45915</v>
+        <v>45922</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>14</v>
@@ -536,37 +560,37 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C8" s="2">
-        <v>45915</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>15</v>
+        <v>45922</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="C9" s="2">
-        <v>45915</v>
+        <v>45922</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{ED579688-13B9-41DF-9417-A11CACC9FD09}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{B6EE4731-DACA-44BD-B321-3D37BDB35EF3}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{726232BE-FFF7-48BF-96A3-E31918FE2BBF}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{4AF10226-85EC-4E10-8D35-ED72C6A663DC}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{17299730-F797-4499-AF48-DD4C0EF94E5D}"/>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{F3E80B10-02B1-4843-8F92-0AA324C35642}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{36F437A8-2D5B-4CD8-86B3-009FFCF55F26}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{AD812E6A-4E8B-4A3B-A8DF-7FBDAA9F4F5F}"/>
+    <hyperlink ref="D7" r:id="rId4" xr:uid="{F5130554-6F9E-44CA-B6D8-2FE659F26A25}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{5CB50CAD-C305-446A-BDF9-A45354753687}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
@@ -574,8 +598,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BC6DA8-A4F2-47AB-9EEC-B9DE3EEA2B23}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45919</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45913</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45917</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45919</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D1" r:id="rId1" xr:uid="{AB476016-1554-4BA9-82BC-ACFADF9F4D82}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF8F8C7-ECA9-4044-81E7-0CA852586859}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -696,6 +763,109 @@
         <v>45905</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C14" s="2">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C15" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C16" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C17" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C18" s="2">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C19" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C20" s="2">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C21" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{78B36FED-FC4F-48FD-B7FE-B84FB456F631}"/>
@@ -703,6 +873,11 @@
     <hyperlink ref="D3" r:id="rId3" xr:uid="{992277C5-361B-4E2A-B687-E1C2C4B5D535}"/>
     <hyperlink ref="D5" r:id="rId4" xr:uid="{99703584-4C05-41F4-A3C0-44F255B253C1}"/>
     <hyperlink ref="D6" r:id="rId5" xr:uid="{E20DDFD9-D127-4AB6-B1B8-09FD68386E74}"/>
+    <hyperlink ref="D16" r:id="rId6" xr:uid="{ED579688-13B9-41DF-9417-A11CACC9FD09}"/>
+    <hyperlink ref="D15" r:id="rId7" xr:uid="{B6EE4731-DACA-44BD-B321-3D37BDB35EF3}"/>
+    <hyperlink ref="D17" r:id="rId8" xr:uid="{726232BE-FFF7-48BF-96A3-E31918FE2BBF}"/>
+    <hyperlink ref="D19" r:id="rId9" xr:uid="{4AF10226-85EC-4E10-8D35-ED72C6A663DC}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{17299730-F797-4499-AF48-DD4C0EF94E5D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itstr\OneDrive\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F82066-C05C-485A-83BB-0FE5CF955F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6562B45A-1678-43B2-B4B9-E2DD59640F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="24">
   <si>
     <t>leader_name</t>
   </si>
@@ -104,6 +105,12 @@
   </si>
   <si>
     <t>Panchayat Raj</t>
+  </si>
+  <si>
+    <t>Ativrushti</t>
+  </si>
+  <si>
+    <t>RC visits</t>
   </si>
 </sst>
 </file>
@@ -457,16 +464,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,117 +487,106 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45922</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45922</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45922</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45922</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C6" s="2">
-        <v>45922</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45922</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="B8" s="2">
-        <v>45915</v>
+        <v>45957</v>
       </c>
       <c r="C8" s="2">
-        <v>45922</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C9" s="2">
-        <v>45922</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>15</v>
+        <v>45964</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{F3E80B10-02B1-4843-8F92-0AA324C35642}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{36F437A8-2D5B-4CD8-86B3-009FFCF55F26}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{AD812E6A-4E8B-4A3B-A8DF-7FBDAA9F4F5F}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{F5130554-6F9E-44CA-B6D8-2FE659F26A25}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{5CB50CAD-C305-446A-BDF9-A45354753687}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{C8C263B1-D009-4613-93FA-B312B71DBB84}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{83BD0E53-F6C2-4158-8AE7-3CF0E5A51EDF}"/>
+    <hyperlink ref="D2" r:id="rId3" xr:uid="{8AF0B708-48A6-4F7A-BB96-EEFAFE1818DE}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{17ED1D5E-C263-4C9B-91B0-90288DD5B419}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{C42C17F5-2DDF-4F18-BC42-5354FC2F63C9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
@@ -598,58 +594,219 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BC6DA8-A4F2-47AB-9EEC-B9DE3EEA2B23}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB255B6-3740-4DCD-B458-A7CFFDD7780C}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>18</v>
+    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B1" s="2">
-        <v>45919</v>
+        <v>45936</v>
       </c>
       <c r="C1" s="2">
-        <v>45913</v>
+        <v>45943</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45936</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>45917</v>
+        <v>45936</v>
       </c>
       <c r="C3" s="2">
-        <v>45919</v>
+        <v>45943</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45936</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45943</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45936</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45943</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D1" r:id="rId1" xr:uid="{AB476016-1554-4BA9-82BC-ACFADF9F4D82}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{AAAE88F0-CD1E-4991-A721-FAA7BDF88751}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{DAB3BD3A-7F01-4935-9323-C9D0D8D74E65}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{8AE8C3EE-84B3-4F14-9F4C-99833DF08366}"/>
+    <hyperlink ref="D1" r:id="rId4" xr:uid="{2EF797A0-2F54-4C20-8CF5-693610CCA549}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF8F8C7-ECA9-4044-81E7-0CA852586859}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BC6DA8-A4F2-47AB-9EEC-B9DE3EEA2B23}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45919</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45913</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45917</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45912</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45923</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45917</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45917</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45917</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45925</v>
+      </c>
+      <c r="C12" s="2">
+        <v>45929</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D1" r:id="rId1" xr:uid="{AB476016-1554-4BA9-82BC-ACFADF9F4D82}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{2DA6CB96-1180-4633-B873-0239436158C6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF8F8C7-ECA9-4044-81E7-0CA852586859}">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -663,7 +820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -677,7 +834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -691,7 +848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -702,7 +859,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -716,7 +873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="20" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -730,7 +887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -741,7 +898,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -752,7 +909,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -763,7 +920,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -774,7 +931,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -788,7 +945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
@@ -802,7 +959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -816,7 +973,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>8</v>
       </c>
@@ -827,7 +984,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -841,7 +998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
@@ -852,7 +1009,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="20" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
@@ -864,6 +1021,201 @@
       </c>
       <c r="D21" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45922</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45922</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C26" s="2">
+        <v>45922</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C27" s="2">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C28" s="2">
+        <v>45922</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C29" s="2">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="20" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45915</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45922</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C32" s="2">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C33" s="2">
+        <v>45929</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C34" s="2">
+        <v>45929</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C35" s="2">
+        <v>45929</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C36" s="2">
+        <v>45929</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C37" s="2">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45922</v>
+      </c>
+      <c r="C38" s="2">
+        <v>45929</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -878,6 +1230,16 @@
     <hyperlink ref="D17" r:id="rId8" xr:uid="{726232BE-FFF7-48BF-96A3-E31918FE2BBF}"/>
     <hyperlink ref="D19" r:id="rId9" xr:uid="{4AF10226-85EC-4E10-8D35-ED72C6A663DC}"/>
     <hyperlink ref="D21" r:id="rId10" xr:uid="{17299730-F797-4499-AF48-DD4C0EF94E5D}"/>
+    <hyperlink ref="D26" r:id="rId11" xr:uid="{F3E80B10-02B1-4843-8F92-0AA324C35642}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{36F437A8-2D5B-4CD8-86B3-009FFCF55F26}"/>
+    <hyperlink ref="D24" r:id="rId13" xr:uid="{AD812E6A-4E8B-4A3B-A8DF-7FBDAA9F4F5F}"/>
+    <hyperlink ref="D28" r:id="rId14" xr:uid="{F5130554-6F9E-44CA-B6D8-2FE659F26A25}"/>
+    <hyperlink ref="D30" r:id="rId15" xr:uid="{5CB50CAD-C305-446A-BDF9-A45354753687}"/>
+    <hyperlink ref="D35" r:id="rId16" xr:uid="{109C6B2A-C11D-4A70-8BCF-0CE6010B00F5}"/>
+    <hyperlink ref="D34" r:id="rId17" xr:uid="{84D8210F-D895-4848-9B44-0BEC1BA61E3F}"/>
+    <hyperlink ref="D33" r:id="rId18" xr:uid="{A1EA902D-7AE0-4C8C-9088-07549026BA63}"/>
+    <hyperlink ref="D36" r:id="rId19" xr:uid="{0285A643-81B9-456D-AF88-5C80D7EDB849}"/>
+    <hyperlink ref="D38" r:id="rId20" xr:uid="{E148E67B-8DCB-41DB-A682-FE0577D70386}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Input/input_leaders.xlsx
+++ b/Input/input_leaders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itstr\OneDrive\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6562B45A-1678-43B2-B4B9-E2DD59640F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27063F3E-5186-4AA2-9CE0-3EDC18CD3E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,10 +492,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C2" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
@@ -506,10 +506,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C3" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
@@ -520,10 +520,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C4" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>5</v>
@@ -534,10 +534,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C5" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>14</v>
@@ -548,10 +548,10 @@
         <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C6" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -559,10 +559,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C7" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>19</v>
@@ -573,10 +573,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="C8" s="2">
-        <v>45964</v>
+        <v>45971</v>
       </c>
     </row>
   </sheetData>
